--- a/documents/capg_proj_section1.xlsx
+++ b/documents/capg_proj_section1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rohit\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1920EC9-29A7-473E-9E8B-6EA9A1AF51E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{F124001B-9FF8-40E9-9788-3DF4154DDFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE6EB65F-6F58-4623-8F70-3E9CD586A436}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="7" xr2:uid="{C3D66DE1-8C8E-4493-BAB2-22CB8F5ED656}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{C3D66DE1-8C8E-4493-BAB2-22CB8F5ED656}"/>
   </bookViews>
   <sheets>
     <sheet name="Guidance &amp; Instructions" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="302">
   <si>
     <t>1. TEST PLAN</t>
   </si>
@@ -887,6 +887,92 @@
   <si>
     <t xml:space="preserve">
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes Application Automation Testing </t>
+  </si>
+  <si>
+    <t>Adhithi Karrolla</t>
+  </si>
+  <si>
+    <t>Covered</t>
+  </si>
+  <si>
+    <t>UI login should work with valid credentials</t>
+  </si>
+  <si>
+    <t>Manual UI Login Testing</t>
+  </si>
+  <si>
+    <t>Create note via UI</t>
+  </si>
+  <si>
+    <t>Manual Create Note Testing</t>
+  </si>
+  <si>
+    <t>Note should appear instantly in UI list after creation</t>
+  </si>
+  <si>
+    <t>Manual UI Validation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>GET /notes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> should return notes list successfully</t>
+    </r>
+  </si>
+  <si>
+    <t>Manual API Testing using Postman</t>
+  </si>
+  <si>
+    <t>UI-created note must appear in API response</t>
+  </si>
+  <si>
+    <t>End-to-End Validation (UI + API)</t>
+  </si>
+  <si>
+    <t>Delete note successfully via API</t>
+  </si>
+  <si>
+    <t>Manual Delete API Testing</t>
+  </si>
+  <si>
+    <t>Deleted note must disappear from UI</t>
+  </si>
+  <si>
+    <t>End-to-End Deletion Validation</t>
+  </si>
+  <si>
+    <t>TC-PERF-01</t>
+  </si>
+  <si>
+    <t>API response time should be less than 2 seconds</t>
+  </si>
+  <si>
+    <t>Manual Performance Validation</t>
+  </si>
+  <si>
+    <t>Negative scenarios for UI and API should be handled properly</t>
+  </si>
+  <si>
+    <t>Negative Testing (UI &amp; API)</t>
   </si>
 </sst>
 </file>
@@ -894,9 +980,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -931,6 +1017,11 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -952,34 +1043,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1315,273 +1396,273 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3DE7513-460D-4528-BEA6-F684F4520CE4}">
   <dimension ref="A1:A61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="80.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1593,282 +1674,261 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D32F19B9-515B-4393-85F3-63978C5B59B0}">
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38.21875" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="18">
+      <c r="A1" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="7"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="10"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2"/>
       <c r="B11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2"/>
       <c r="B12" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2"/>
       <c r="B13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2"/>
       <c r="B14" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2"/>
       <c r="B15" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2"/>
       <c r="B16" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2"/>
       <c r="B17" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2"/>
       <c r="B18" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:2">
+      <c r="A30" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B30" s="4"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="4">
         <v>46146</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="4">
         <v>46149</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:2">
+      <c r="A34" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="4"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
         <v>79</v>
       </c>
-      <c r="B37" s="4"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
         <v>81</v>
       </c>
       <c r="B40" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
+    <row r="41" spans="1:2">
       <c r="B41" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2">
       <c r="B42" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="43" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
         <v>82</v>
       </c>
       <c r="B44" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2">
       <c r="B45" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
+    <row r="46" spans="1:2">
       <c r="B46" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="6"/>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1881,30 +1941,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025C1F45-4255-40C3-BEB9-29547D6C800F}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" style="10" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
     <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="63.88671875" customWidth="1"/>
     <col min="4" max="4" width="36.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>102</v>
       </c>
       <c r="B2" t="s">
@@ -1917,8 +1977,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>103</v>
       </c>
       <c r="B3" t="s">
@@ -1931,8 +1991,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>104</v>
       </c>
       <c r="B4" t="s">
@@ -1945,73 +2005,73 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" t="s">
         <v>121</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" t="s">
         <v>122</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" t="s">
         <v>125</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" t="s">
         <v>130</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2023,7 +2083,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78FC90AF-B44B-4DEE-9843-221C8EB05EB3}">
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.5546875" customWidth="1"/>
     <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
@@ -2033,33 +2093,33 @@
     <col min="6" max="6" width="58.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>147</v>
       </c>
@@ -2085,23 +2145,22 @@
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="E3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E4" s="11" t="s">
+    <row r="4" spans="1:8">
+      <c r="E4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="E5" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>148</v>
       </c>
@@ -2127,23 +2186,22 @@
         <v>160</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="E8" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E9" s="11" t="s">
+    <row r="9" spans="1:8">
+      <c r="E9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E10" s="11" t="s">
+    <row r="10" spans="1:8">
+      <c r="E10" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>149</v>
       </c>
@@ -2169,177 +2227,172 @@
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E13" s="11" t="s">
+    <row r="13" spans="1:8">
+      <c r="E13" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
         <v>169</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" t="s">
         <v>170</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" t="s">
         <v>171</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" t="s">
         <v>172</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" t="s">
         <v>159</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="E16" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E17" s="14" t="s">
+    <row r="17" spans="1:8">
+      <c r="E17" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
         <v>173</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" t="s">
         <v>174</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" t="s">
         <v>191</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" t="s">
         <v>175</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" t="s">
         <v>159</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E20" s="14" t="s">
+    <row r="20" spans="1:8">
+      <c r="E20" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E21" s="14" t="s">
+    <row r="21" spans="1:8">
+      <c r="E21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" t="s">
         <v>177</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" t="s">
         <v>126</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" t="s">
         <v>194</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" t="s">
         <v>178</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="14" t="s">
+      <c r="H23" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E24" s="14" t="s">
+    <row r="24" spans="1:8">
+      <c r="E24" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
         <v>179</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" t="s">
         <v>108</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" t="s">
         <v>180</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" t="s">
         <v>181</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" t="s">
         <v>196</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" t="s">
         <v>182</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" t="s">
         <v>159</v>
       </c>
-      <c r="H26" s="14" t="s">
+      <c r="H26" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E27" s="14" t="s">
+    <row r="27" spans="1:8">
+      <c r="E27" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="14" t="s">
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
         <v>183</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" t="s">
         <v>185</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" t="s">
         <v>198</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" t="s">
         <v>186</v>
       </c>
-      <c r="G29" s="14" t="s">
+      <c r="G29" t="s">
         <v>187</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="H29" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="E30" t="s">
         <v>199</v>
       </c>
@@ -2352,7 +2405,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CC977C9-9325-44D7-AE93-769D9BB19E9D}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
     <col min="2" max="2" width="14.109375" customWidth="1"/>
@@ -2360,21 +2413,21 @@
     <col min="4" max="4" width="31.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>204</v>
       </c>
@@ -2388,12 +2441,12 @@
         <v>222</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="C3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>206</v>
       </c>
@@ -2407,12 +2460,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="C5" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>208</v>
       </c>
@@ -2426,12 +2479,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="C7" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>209</v>
       </c>
@@ -2445,7 +2498,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>210</v>
       </c>
@@ -2467,30 +2520,30 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{710D8237-164A-4E0E-B427-76FBD3D99BF0}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
     <col min="3" max="3" width="35.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="5" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>147</v>
       </c>
@@ -2507,7 +2560,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>148</v>
       </c>
@@ -2524,7 +2577,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>149</v>
       </c>
@@ -2541,7 +2594,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>169</v>
       </c>
@@ -2558,7 +2611,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>173</v>
       </c>
@@ -2575,7 +2628,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>176</v>
       </c>
@@ -2592,7 +2645,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -2609,7 +2662,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>183</v>
       </c>
@@ -2634,128 +2687,179 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8174C34E-9E0E-48A3-9454-EA818E9ADBD9}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" customWidth="1"/>
     <col min="4" max="4" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" ht="28.8">
+      <c r="A2" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="B2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="8" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="C2" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.8">
+      <c r="A3" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="B3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="C3" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="28.8">
+      <c r="A4" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="B4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="8" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="C4" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="43.2">
+      <c r="A5" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="B5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="8" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="C5" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="43.2">
+      <c r="A6" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="B6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="C6" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8">
+      <c r="A7" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="B7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="8" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="C7" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="43.2">
+      <c r="A8" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="B8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="8" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="C8" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="43.2">
+      <c r="A9" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="B9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B9" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="43.2">
+      <c r="A10" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="B10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="8" t="s">
         <v>183</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -2766,164 +2870,182 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B113F62B-0C26-4862-8BD3-B0300A49D5E5}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.88671875" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="2" max="2" width="35.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B1" s="15"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="15"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="B2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>255</v>
       </c>
-      <c r="B3" s="15"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>256</v>
       </c>
-      <c r="B4" s="15"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="15"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="B5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B7" s="15"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>258</v>
       </c>
-      <c r="B8" s="15"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="B8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>259</v>
       </c>
-      <c r="B9" s="15"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="B9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>260</v>
       </c>
-      <c r="B10" s="15"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="B10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>261</v>
       </c>
-      <c r="B11" s="15"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>262</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="7" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B14" s="15"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>265</v>
       </c>
-      <c r="B15" s="15"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>266</v>
       </c>
-      <c r="B16" s="15"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>267</v>
       </c>
-      <c r="B17" s="15"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>268</v>
       </c>
-      <c r="B18" s="15"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>269</v>
       </c>
-      <c r="B19" s="15"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
         <v>270</v>
       </c>
-      <c r="B20" s="15"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>271</v>
       </c>
-      <c r="B21" s="15"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B23" s="15"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
         <v>273</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
         <v>275</v>
       </c>
-      <c r="B25" s="15"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
         <v>276</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
+    <row r="28" spans="1:2">
+      <c r="A28" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B28" s="15"/>
-    </row>
-    <row r="31" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
+    </row>
+    <row r="31" spans="1:2" ht="28.8">
+      <c r="A31" s="3" t="s">
         <v>279</v>
       </c>
     </row>
